--- a/Excel Practice @ Day 03 New finish.xlsx
+++ b/Excel Practice @ Day 03 New finish.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e8b4505378d7763/Desktop/Codegnan Excel Practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{E0F28121-1C79-4240-84FC-B6F105CEFE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B646F1D3-E509-4F47-8C23-643138E16E9C}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{E0F28121-1C79-4240-84FC-B6F105CEFE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB243CE7-72A1-4754-AB19-75C05FDCC5DD}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="237">
   <si>
     <t>Patient_ID</t>
   </si>
@@ -1033,6 +1033,9 @@
   </si>
   <si>
     <t>Management Review</t>
+  </si>
+  <si>
+    <t>"female"</t>
   </si>
 </sst>
 </file>
@@ -1234,23 +1237,23 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1268,6 +1271,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1555,9 +1562,62 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{65EFE936-D7FE-421F-8FA2-9F6EBC50FEF9}">
+  <we:reference id="wa200005271" version="2.4.4.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200005271" version="2.4.4.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions val="1"/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_AI_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_ASK</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_CHOICE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{0B4E55D2-BED8-45C4-BCE3-A37C2D108A44}">
+  <we:reference id="wa104381071" version="2.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA104381071" version="2.0.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:Z66"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -1585,7 +1645,7 @@
     <col min="24" max="24" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1">
+    <row r="1" spans="1:26" ht="15" thickBot="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1659,7 +1719,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="15" thickTop="1">
+    <row r="2" spans="1:26" ht="15" thickTop="1">
       <c r="A2" s="18" t="s">
         <v>13</v>
       </c>
@@ -1744,7 +1804,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:26">
       <c r="A3" s="23" t="s">
         <v>14</v>
       </c>
@@ -1829,7 +1889,7 @@
         <v>MR</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:26">
       <c r="A4" s="27" t="s">
         <v>15</v>
       </c>
@@ -1914,7 +1974,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:26">
       <c r="A5" s="23" t="s">
         <v>16</v>
       </c>
@@ -1999,7 +2059,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:26">
       <c r="A6" s="27" t="s">
         <v>17</v>
       </c>
@@ -2084,7 +2144,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:26">
       <c r="A7" s="23" t="s">
         <v>18</v>
       </c>
@@ -2169,7 +2229,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:26">
       <c r="A8" s="27" t="s">
         <v>19</v>
       </c>
@@ -2254,7 +2314,7 @@
         <v>MR</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:26">
       <c r="A9" s="23" t="s">
         <v>20</v>
       </c>
@@ -2338,8 +2398,11 @@
         <f t="shared" si="1"/>
         <v>No Review</v>
       </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="Z9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="27" t="s">
         <v>21</v>
       </c>
@@ -2424,7 +2487,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:26">
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
@@ -2509,7 +2572,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:26">
       <c r="A12" s="27" t="s">
         <v>23</v>
       </c>
@@ -2594,7 +2657,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:26">
       <c r="A13" s="23" t="s">
         <v>24</v>
       </c>
@@ -2679,7 +2742,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:26">
       <c r="A14" s="27" t="s">
         <v>25</v>
       </c>
@@ -2764,7 +2827,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:26">
       <c r="A15" s="23" t="s">
         <v>26</v>
       </c>
@@ -2849,7 +2912,7 @@
         <v>No Review</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:26">
       <c r="A16" s="27" t="s">
         <v>27</v>
       </c>
@@ -5262,6 +5325,17 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z9" xr:uid="{E547A38A-A36E-4C87-994F-6DE728302A01}">
+      <formula1>"""male"",""female"""</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z11" xr:uid="{C0E866DE-D70D-48EE-93DD-96662597591B}">
+      <formula1>10</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC8" xr:uid="{54E95D85-199D-4C3E-B46A-01FA002BFEDF}">
+      <formula1>10</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
